--- a/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440471</t>
+          <t>440134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459828</t>
+          <t>459500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280756</t>
+          <t>280769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296483</t>
+          <t>296708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728381</t>
+          <t>727454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>752799</t>
+          <t>753205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31157</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54904</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333767</t>
+          <t>333446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352099</t>
+          <t>352253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339300</t>
+          <t>338953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358258</t>
+          <t>357547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680868</t>
+          <t>679904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706858</t>
+          <t>706375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65157</t>
+          <t>67201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495326</t>
+          <t>494071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517672</t>
+          <t>517147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138943</t>
+          <t>140269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155413</t>
+          <t>156187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642102</t>
+          <t>640058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>667623</t>
+          <t>669107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81027</t>
+          <t>80145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118300</t>
+          <t>117919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74759</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135107</t>
+          <t>131343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182793</t>
+          <t>182320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1116512</t>
+          <t>1116893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1153785</t>
+          <t>1154667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639526</t>
+          <t>641915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>671263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1766305</t>
+          <t>1766778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1813991</t>
+          <t>1817755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65519</t>
+          <t>64039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60112</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>94372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309728</t>
+          <t>308875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330751</t>
+          <t>331673</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>503233</t>
+          <t>504713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>531517</t>
+          <t>531954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822738</t>
+          <t>824091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>858351</t>
+          <t>858816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>92732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134775</t>
+          <t>133952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>103499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148667</t>
+          <t>145972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273965</t>
+          <t>273671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289293</t>
+          <t>289496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1112757</t>
+          <t>1113580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1154554</t>
+          <t>1154800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1396075</t>
+          <t>1398770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1440546</t>
+          <t>1441243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190953</t>
+          <t>191496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>247634</t>
+          <t>250241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>240406</t>
+          <t>240748</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303709</t>
+          <t>303850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>445998</t>
+          <t>444082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>532825</t>
+          <t>535894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3013279</t>
+          <t>3010672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3069960</t>
+          <t>3069417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3070139</t>
+          <t>3069998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3133442</t>
+          <t>3133100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6101936</t>
+          <t>6098867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6188763</t>
+          <t>6190679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39742</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40534</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72658</t>
+          <t>75416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393139</t>
+          <t>393819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418556</t>
+          <t>418111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274712</t>
+          <t>274659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296861</t>
+          <t>297914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679007</t>
+          <t>676249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711131</t>
+          <t>710538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41466</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>36518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>72004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377331</t>
+          <t>376154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400620</t>
+          <t>399710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299610</t>
+          <t>300546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320728</t>
+          <t>319403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>684848</t>
+          <t>683857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714755</t>
+          <t>714772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57506</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94176</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80454</t>
+          <t>81882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121342</t>
+          <t>123724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535239</t>
+          <t>535073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571909</t>
+          <t>572430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222595</t>
+          <t>223185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241739</t>
+          <t>242671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767255</t>
+          <t>764873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>808143</t>
+          <t>806715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105537</t>
+          <t>106954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152621</t>
+          <t>154284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81285</t>
+          <t>81916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120455</t>
+          <t>118248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198998</t>
+          <t>198470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257937</t>
+          <t>257511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1006388</t>
+          <t>1004725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1053472</t>
+          <t>1052055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>646202</t>
+          <t>648409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685372</t>
+          <t>684741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1667730</t>
+          <t>1668156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1726669</t>
+          <t>1727197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>58840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>87897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125239</t>
+          <t>127715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>129310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176996</t>
+          <t>174913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450133</t>
+          <t>449638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475719</t>
+          <t>474957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636283</t>
+          <t>633807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>675065</t>
+          <t>673625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1093004</t>
+          <t>1095087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1140511</t>
+          <t>1140690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103524</t>
+          <t>105217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147969</t>
+          <t>147397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124626</t>
+          <t>123340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172811</t>
+          <t>169520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232708</t>
+          <t>232950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252277</t>
+          <t>252360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>961382</t>
+          <t>961954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1005827</t>
+          <t>1004134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1202374</t>
+          <t>1205665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250559</t>
+          <t>1251845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>292312</t>
+          <t>290954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367146</t>
+          <t>363168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368047</t>
+          <t>368714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>448571</t>
+          <t>449364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>684186</t>
+          <t>680547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>788610</t>
+          <t>787899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3051597</t>
+          <t>3055575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3126431</t>
+          <t>3127789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3099660</t>
+          <t>3098867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3180184</t>
+          <t>3179517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6178364</t>
+          <t>6179075</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6282788</t>
+          <t>6286427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52455</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393479</t>
+          <t>392807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410539</t>
+          <t>410931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>316699</t>
+          <t>317249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335255</t>
+          <t>335843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717082</t>
+          <t>718740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742784</t>
+          <t>743803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>31241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54173</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345398</t>
+          <t>345986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364100</t>
+          <t>364623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341536</t>
+          <t>341074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359384</t>
+          <t>359433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694351</t>
+          <t>694663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720274</t>
+          <t>718766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>53258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>70449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468041</t>
+          <t>468656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493598</t>
+          <t>493887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141790</t>
+          <t>142365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158919</t>
+          <t>158897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616493</t>
+          <t>617587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647777</t>
+          <t>647785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67298</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105673</t>
+          <t>105879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56595</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91171</t>
+          <t>90290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134690</t>
+          <t>135960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182489</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040849</t>
+          <t>1040643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1079224</t>
+          <t>1077620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733777</t>
+          <t>734658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>768353</t>
+          <t>768452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1788981</t>
+          <t>1786397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1836780</t>
+          <t>1835510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40499</t>
+          <t>39832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68267</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64734</t>
+          <t>63106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114637</t>
+          <t>111117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160921</t>
+          <t>159951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>547263</t>
+          <t>544889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>575031</t>
+          <t>575698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635732</t>
+          <t>634903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670372</t>
+          <t>672000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1189715</t>
+          <t>1190685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1235999</t>
+          <t>1239519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81610</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122924</t>
+          <t>123524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100398</t>
+          <t>99352</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141120</t>
+          <t>143753</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256188</t>
+          <t>256356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273551</t>
+          <t>273466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>957097</t>
+          <t>956497</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>998411</t>
+          <t>998806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1224221</t>
+          <t>1221588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264943</t>
+          <t>1265989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209909</t>
+          <t>206418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>270500</t>
+          <t>267480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>274639</t>
+          <t>275496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>345842</t>
+          <t>345040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>500382</t>
+          <t>499763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>589512</t>
+          <t>593881</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3098495</t>
+          <t>3101515</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3159086</t>
+          <t>3162577</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3178707</t>
+          <t>3179509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3249910</t>
+          <t>3249053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6304033</t>
+          <t>6299664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6393163</t>
+          <t>6393782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71384</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30957</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>53177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>81987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>118791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428456</t>
+          <t>428317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455968</t>
+          <t>457108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>392533</t>
+          <t>391423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413643</t>
+          <t>413136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>826651</t>
+          <t>825649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862311</t>
+          <t>862453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57008</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45060</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393382</t>
+          <t>393906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418182</t>
+          <t>419009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335721</t>
+          <t>335696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354089</t>
+          <t>354147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736256</t>
+          <t>735669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>767124</t>
+          <t>766806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114641</t>
+          <t>116554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135925</t>
+          <t>136548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552970</t>
+          <t>551057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644326</t>
+          <t>642771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132746</t>
+          <t>133280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148820</t>
+          <t>149175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>697938</t>
+          <t>697315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>801781</t>
+          <t>789737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129661</t>
+          <t>128733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174067</t>
+          <t>175641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107113</t>
+          <t>109751</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>640373</t>
+          <t>615600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257671</t>
+          <t>256676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>873400</t>
+          <t>1026051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855776</t>
+          <t>854202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900182</t>
+          <t>901110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333835</t>
+          <t>358608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>867095</t>
+          <t>864457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1130651</t>
+          <t>978000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1746380</t>
+          <t>1747375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79274</t>
+          <t>79189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115761</t>
+          <t>115088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96170</t>
+          <t>91968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154610</t>
+          <t>153221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183862</t>
+          <t>183078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257841</t>
+          <t>256818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>351982</t>
+          <t>352655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388469</t>
+          <t>388554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>681596</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>740036</t>
+          <t>744238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046108</t>
+          <t>1047131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1120087</t>
+          <t>1120871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26229</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126695</t>
+          <t>126281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160786</t>
+          <t>161323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136714</t>
+          <t>136263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179790</t>
+          <t>178559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212371</t>
+          <t>212563</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231695</t>
+          <t>231897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600226</t>
+          <t>599689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634317</t>
+          <t>634731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>819822</t>
+          <t>821053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>862898</t>
+          <t>863349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>346400</t>
+          <t>331111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>481146</t>
+          <t>482274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>478256</t>
+          <t>478668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1221838</t>
+          <t>1184307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>889277</t>
+          <t>890530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1639100</t>
+          <t>1655057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2872880</t>
+          <t>2871752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3007626</t>
+          <t>3022915</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2341221</t>
+          <t>2378752</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3084803</t>
+          <t>3084391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5277986</t>
+          <t>5262029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6027809</t>
+          <t>6026556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>51176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440134</t>
+          <t>440971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459500</t>
+          <t>459071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280769</t>
+          <t>281308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296708</t>
+          <t>296896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727454</t>
+          <t>728252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753205</t>
+          <t>752285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55868</t>
+          <t>56470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333446</t>
+          <t>334490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352253</t>
+          <t>352597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338953</t>
+          <t>338182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357547</t>
+          <t>357310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679904</t>
+          <t>679302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706375</t>
+          <t>704972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67201</t>
+          <t>66491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494071</t>
+          <t>494276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517147</t>
+          <t>516256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140269</t>
+          <t>140106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156187</t>
+          <t>155941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640058</t>
+          <t>640768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>669107</t>
+          <t>667734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80145</t>
+          <t>82023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117919</t>
+          <t>119585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>45072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131343</t>
+          <t>132701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182320</t>
+          <t>182701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1116893</t>
+          <t>1115227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1154667</t>
+          <t>1152789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641915</t>
+          <t>639529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671263</t>
+          <t>669213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1766778</t>
+          <t>1766397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1817755</t>
+          <t>1816397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>35736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64039</t>
+          <t>61947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>61507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>96051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308875</t>
+          <t>308925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331673</t>
+          <t>330121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>504713</t>
+          <t>506805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>531954</t>
+          <t>533016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824091</t>
+          <t>822412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>858816</t>
+          <t>856956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133952</t>
+          <t>130574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103499</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145972</t>
+          <t>146901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273671</t>
+          <t>273225</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289496</t>
+          <t>289573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1113580</t>
+          <t>1116958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1154800</t>
+          <t>1156378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1398770</t>
+          <t>1397841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1441243</t>
+          <t>1440229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191496</t>
+          <t>189376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>250241</t>
+          <t>245098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>240748</t>
+          <t>239019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303850</t>
+          <t>303769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>444082</t>
+          <t>448514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535894</t>
+          <t>536783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3010672</t>
+          <t>3015815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3069417</t>
+          <t>3071537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3069998</t>
+          <t>3070079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3133100</t>
+          <t>3134829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6098867</t>
+          <t>6097978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6190679</t>
+          <t>6186247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75416</t>
+          <t>73841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393819</t>
+          <t>394612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418111</t>
+          <t>418801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274659</t>
+          <t>274417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297914</t>
+          <t>297375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676249</t>
+          <t>677824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710538</t>
+          <t>710186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72004</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376154</t>
+          <t>378416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399710</t>
+          <t>400284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300546</t>
+          <t>299194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319403</t>
+          <t>320357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683857</t>
+          <t>685138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714772</t>
+          <t>714990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>92075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>37109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81882</t>
+          <t>80994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123724</t>
+          <t>121742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535073</t>
+          <t>537340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572430</t>
+          <t>572327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223185</t>
+          <t>222073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242671</t>
+          <t>241484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764873</t>
+          <t>766855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>806715</t>
+          <t>807603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106954</t>
+          <t>106788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154284</t>
+          <t>149843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>79772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118248</t>
+          <t>118301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198470</t>
+          <t>194983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257511</t>
+          <t>257918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004725</t>
+          <t>1009166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1052055</t>
+          <t>1052221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648409</t>
+          <t>648356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684741</t>
+          <t>686885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1668156</t>
+          <t>1667749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1727197</t>
+          <t>1730684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87897</t>
+          <t>86405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>126015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174913</t>
+          <t>174581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449638</t>
+          <t>450705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474957</t>
+          <t>475829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>633807</t>
+          <t>635507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>673625</t>
+          <t>675117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1095087</t>
+          <t>1095419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1140690</t>
+          <t>1142305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105217</t>
+          <t>106590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147397</t>
+          <t>148093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123340</t>
+          <t>121793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169520</t>
+          <t>170247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232950</t>
+          <t>231740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252360</t>
+          <t>252332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>961954</t>
+          <t>961258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1004134</t>
+          <t>1002761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205665</t>
+          <t>1204938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1251845</t>
+          <t>1253392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>290954</t>
+          <t>285729</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>363168</t>
+          <t>361184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368714</t>
+          <t>367982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>449364</t>
+          <t>445819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>680547</t>
+          <t>679038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>787899</t>
+          <t>788821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3055575</t>
+          <t>3057559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3127789</t>
+          <t>3133014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3098867</t>
+          <t>3102412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3179517</t>
+          <t>3180249</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6179075</t>
+          <t>6178153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6286427</t>
+          <t>6287936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25734</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>50927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392807</t>
+          <t>393738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410931</t>
+          <t>411182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>317249</t>
+          <t>316660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335843</t>
+          <t>335143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718740</t>
+          <t>718610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743803</t>
+          <t>742232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345986</t>
+          <t>346185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364623</t>
+          <t>364308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341074</t>
+          <t>341304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359433</t>
+          <t>359616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694663</t>
+          <t>692971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718766</t>
+          <t>718743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70449</t>
+          <t>68644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468656</t>
+          <t>467793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493887</t>
+          <t>492444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142365</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158897</t>
+          <t>158834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617587</t>
+          <t>619392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647785</t>
+          <t>646432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68902</t>
+          <t>69649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105879</t>
+          <t>106070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90290</t>
+          <t>89563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135960</t>
+          <t>133682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040643</t>
+          <t>1040452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1077620</t>
+          <t>1076873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734658</t>
+          <t>735385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>768452</t>
+          <t>767032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1786397</t>
+          <t>1785655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1835510</t>
+          <t>1837788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39832</t>
+          <t>40494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>69634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>65884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100203</t>
+          <t>101531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111117</t>
+          <t>114121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159951</t>
+          <t>161288</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544889</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>575698</t>
+          <t>575036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634903</t>
+          <t>633575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672000</t>
+          <t>669222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190685</t>
+          <t>1189348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1239519</t>
+          <t>1236515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>81334</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123524</t>
+          <t>120851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>99497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143753</t>
+          <t>144726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256356</t>
+          <t>256951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273466</t>
+          <t>273209</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>956497</t>
+          <t>959170</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>998806</t>
+          <t>998687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1221588</t>
+          <t>1220615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1265989</t>
+          <t>1265844</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206418</t>
+          <t>209350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>267480</t>
+          <t>268737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275496</t>
+          <t>271651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>345040</t>
+          <t>345873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>499763</t>
+          <t>500204</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593881</t>
+          <t>597027</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3101515</t>
+          <t>3100258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3162577</t>
+          <t>3159645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3179509</t>
+          <t>3178676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3249053</t>
+          <t>3252898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6299664</t>
+          <t>6296518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6393782</t>
+          <t>6393341</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71523</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53177</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>98143</t>
+          <t>104100</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>86422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118791</t>
+          <t>124273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>442786</t>
+          <t>482576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428317</t>
+          <t>466821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457108</t>
+          <t>495881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>403511</t>
+          <t>441586</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391423</t>
+          <t>429585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413136</t>
+          <t>451101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>846297</t>
+          <t>924162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>825649</t>
+          <t>903989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862453</t>
+          <t>941840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>499840</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>499840</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>499840</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>444600</t>
+          <t>485410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>444600</t>
+          <t>485410</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>444600</t>
+          <t>485410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>944440</t>
+          <t>1028262</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>944440</t>
+          <t>1028262</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>944440</t>
+          <t>1028262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45085</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77871</t>
+          <t>83622</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95502</t>
+          <t>102763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>407795</t>
+          <t>436400</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393906</t>
+          <t>420803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419009</t>
+          <t>447807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>345506</t>
+          <t>382407</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335696</t>
+          <t>371387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354147</t>
+          <t>390858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>753300</t>
+          <t>818807</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735669</t>
+          <t>799666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>766806</t>
+          <t>832676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450390</t>
+          <t>481243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450390</t>
+          <t>481243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450390</t>
+          <t>481243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380781</t>
+          <t>421186</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380781</t>
+          <t>421186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380781</t>
+          <t>421186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>831171</t>
+          <t>902429</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>831171</t>
+          <t>902429</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>831171</t>
+          <t>902429</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>58022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116554</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>92417</t>
+          <t>98908</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136548</t>
+          <t>117860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>599322</t>
+          <t>399025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>551057</t>
+          <t>382318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642771</t>
+          <t>412872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142124</t>
+          <t>159783</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133280</t>
+          <t>149990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149175</t>
+          <t>167054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>741446</t>
+          <t>558807</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>697315</t>
+          <t>539855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>789737</t>
+          <t>574779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667611</t>
+          <t>470894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667611</t>
+          <t>470894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667611</t>
+          <t>470894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166252</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166252</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166252</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833863</t>
+          <t>657715</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833863</t>
+          <t>657715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833863</t>
+          <t>657715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>150806</t>
+          <t>165998</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128733</t>
+          <t>141734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175641</t>
+          <t>190721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>100914</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109751</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>615600</t>
+          <t>118781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>445257</t>
+          <t>266913</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256676</t>
+          <t>240952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1026051</t>
+          <t>297153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879037</t>
+          <t>958905</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854202</t>
+          <t>934182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>901110</t>
+          <t>983169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>679758</t>
+          <t>756011</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358608</t>
+          <t>738144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>864457</t>
+          <t>768922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1558794</t>
+          <t>1714916</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>978000</t>
+          <t>1684676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1747375</t>
+          <t>1740877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029843</t>
+          <t>1124903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029843</t>
+          <t>1124903</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029843</t>
+          <t>1124903</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>974208</t>
+          <t>856925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>974208</t>
+          <t>856925</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>974208</t>
+          <t>856925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2004051</t>
+          <t>1981829</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2004051</t>
+          <t>1981829</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2004051</t>
+          <t>1981829</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95548</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>82413</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115088</t>
+          <t>121483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>131350</t>
+          <t>148764</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91968</t>
+          <t>131956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>165312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>226898</t>
+          <t>249379</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183078</t>
+          <t>224480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>274289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>372195</t>
+          <t>460463</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352655</t>
+          <t>439595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388554</t>
+          <t>478665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>704856</t>
+          <t>676433</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>659885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744238</t>
+          <t>693241</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1077051</t>
+          <t>1136895</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1047131</t>
+          <t>1111985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1120871</t>
+          <t>1161794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>83,81%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>467743</t>
+          <t>561078</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>467743</t>
+          <t>561078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>467743</t>
+          <t>561078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836206</t>
+          <t>825197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836206</t>
+          <t>825197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836206</t>
+          <t>825197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1303949</t>
+          <t>1386274</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1303949</t>
+          <t>1386274</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1303949</t>
+          <t>1386274</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>142297</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126281</t>
+          <t>138190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>177640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>156432</t>
+          <t>174408</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136263</t>
+          <t>150732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>198663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>224466</t>
+          <t>218036</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212563</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231897</t>
+          <t>225409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>618715</t>
+          <t>686862</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>599689</t>
+          <t>666279</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634731</t>
+          <t>705729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>843180</t>
+          <t>904898</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>821053</t>
+          <t>880643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>863349</t>
+          <t>928574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761012</t>
+          <t>843919</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761012</t>
+          <t>843919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761012</t>
+          <t>843919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999612</t>
+          <t>1079306</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999612</t>
+          <t>1079306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999612</t>
+          <t>1079306</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>428427</t>
+          <t>460953</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>331111</t>
+          <t>418093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>482274</t>
+          <t>502916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>668590</t>
+          <t>516377</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>478668</t>
+          <t>479840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1184307</t>
+          <t>551331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1097018</t>
+          <t>977329</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>890530</t>
+          <t>925435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655057</t>
+          <t>1034024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2925599</t>
+          <t>2955405</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2871752</t>
+          <t>2913442</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3022915</t>
+          <t>2998265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2894469</t>
+          <t>3103081</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2378752</t>
+          <t>3068127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3084391</t>
+          <t>3139618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5820068</t>
+          <t>6058486</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5262029</t>
+          <t>6001791</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6026556</t>
+          <t>6110380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3354026</t>
+          <t>3416358</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3354026</t>
+          <t>3416358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3354026</t>
+          <t>3416358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3563059</t>
+          <t>3619458</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3563059</t>
+          <t>3619458</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3563059</t>
+          <t>3619458</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6917086</t>
+          <t>7035815</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6917086</t>
+          <t>7035815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6917086</t>
+          <t>7035815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
